--- a/jpcore-r4/main/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="650">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -320,16 +320,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -455,7 +455,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -491,7 +491,15 @@
 このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
-    <t>これは業務IDであって、リソースに対するIDではない。</t>
+    <t xml:space="preserve">これは業務IDであって、リソースに対するIDではない。  
+Slice定義は下記のようになる。  
+[Sliceで定義される識別子]  
+　- rpNumber : 処方箋内部の剤グループとしてのRp番号  
+　- orderInRp : 同一RP番号（剤グループ）での薬剤の表記順  
+　- requestIdentifier : 処方オーダに対するID  
+　- prescriptionIdentifierCommon : 全国で⼀意になる発番ルールにもとづき発行される処方箋ID  
+[invariantで定義される識別子]  
+　- jp-inv-local-prescriptionid : 医療機関毎に管理される処方箋に対するID  </t>
   </si>
   <si>
     <t xml:space="preserve">value:system}
@@ -501,6 +509,10 @@
     <t>open</t>
   </si>
   <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+jp-inv-local-prescriptionid:施設処方箋IDを記述する場合には、identifier.systemは、'urn:oid:1.2.392.100495.20.3.11.[1+施設番号10桁]'でなければならない。 {system.all(substring(0,31)!='urn:oid:1.2.392.100495.20.3.11.' or substring(31).matches('^1(0[1-9]|[1-3][0-9]|4[0-7])([0-9])([0-9]{7})$'))}</t>
+  </si>
+  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -581,19 +593,19 @@
     <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
   </si>
   <si>
-    <t>この識別子の目的。 / The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -615,22 +627,22 @@
 </t>
   </si>
   <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -651,16 +663,16 @@
     <t>Rp番号(剤グループ番号)についてのsystem値</t>
   </si>
   <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
-  </si>
-  <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
+  </si>
+  <si>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -709,7 +721,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -734,10 +746,10 @@
     <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
   </si>
   <si>
-    <t>識別子を発行/管理する組織。 / Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>識別子は、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -749,100 +761,100 @@
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon</t>
-  </si>
-  <si>
-    <t>requestIdentifierCommon</t>
+    <t>MedicationRequest.identifier:requestIdentifier</t>
+  </si>
+  <si>
+    <t>requestIdentifier</t>
+  </si>
+  <si>
+    <t>処方オーダに対するID</t>
+  </si>
+  <si>
+    <t>薬剤をオーダする単位としての処方依頼に対するID。MedicationRequestは単一の薬剤でインスタンスが作成される。</t>
+  </si>
+  <si>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。 / This is a business identifier, not a resource identifier.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.use</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.system</t>
+  </si>
+  <si>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.value</t>
+  </si>
+  <si>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.period</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.assigner</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon</t>
+  </si>
+  <si>
+    <t>prescriptionIdentifierCommon</t>
   </si>
   <si>
     <t>処方箋に対するID</t>
   </si>
   <si>
-    <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。system 要素には、保険医療機関番号を含む処方箋ID（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.use</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.system</t>
-  </si>
-  <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.use</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.system</t>
   </si>
   <si>
     <t>urn:oid:1.2.392.100495.20.3.11</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.value</t>
-  </si>
-  <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.period</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.assigner</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier</t>
-  </si>
-  <si>
-    <t>requestIdentifier</t>
-  </si>
-  <si>
-    <t>処方オーダに対するID</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方依頼に対するID。MedicationRequestは単一の薬剤でインスタンスが作成される。</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.use</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.system</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.value</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.period</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.assigner</t>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.value</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.period</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.assigner</t>
   </si>
   <si>
     <t>MedicationRequest.status</t>
@@ -1028,8 +1040,7 @@
     <t>What medication was supplied　医薬品</t>
   </si>
   <si>
-    <t>Identifies the medication that was administered. This is either a link to a resource representing the details of the medication or a simple attribute carrying a code that identifies the medication from a known list of medications.  
-投与された薬剤を識別する。既知の薬のリストから薬を識別するコード情報を設定する。</t>
+    <t>医薬品の識別情報は必須でありmedicationReference.referenceが必ず存在しなければならない、JP Coreでは注射の医薬品情報は単一薬剤の場合も Medicationリソースとして記述し、medicationCodeableConceptは使用しない。参照するMedicationリソースは、MedicationRequest.contained属性に内包することが望ましいが、外部参照としても良い。</t>
   </si>
   <si>
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the medication resource is recommended.  For example, if you require form or lot number, then you must reference the Medication resource.  
@@ -1455,13 +1466,19 @@
 </t>
   </si>
   <si>
-    <t>薬の服用方法・服用した方法、または服用すべき方法</t>
+    <t>薬をどのように服用すべきか / How the medication should be taken</t>
+  </si>
+  <si>
+    <t>患者が薬をどのように使用するかを示します。 / Indicates how the medication is to be used by the patient.</t>
   </si>
   <si>
     <t>薬の要求には、経口投与または静脈内または筋肉内の用量のオプションが含まれる場合があります。たとえば、「吐き気に必要に応じて、1日に2回Ondansetron 8mgまたはIV」または「Compazine®（プロクロロペラジン）5-10mg POまたは25mg PR BID PRN吐き気または嘔吐」。これらの場合、グループ化できる2つの投薬要求が作成されます。使用する投与経路の決定は、用量が必要な時点での患者の状態に基づいています。 / There are examples where a medication request may include the option of an oral dose or an Intravenous or Intramuscular dose.  For example, "Ondansetron 8mg orally or IV twice a day as needed for nausea" or "Compazine® (prochlorperazine) 5-10mg PO or 25mg PR bid prn nausea or vomiting".  In these cases, two medication requests would be created that could be grouped together.  The decision on which dose and route of administration to use is based on the patient's condition at the time the dose is needed.</t>
   </si>
   <si>
-    <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=INT]</t>
+    <t>Request.occurrence[x]</t>
+  </si>
+  <si>
+    <t>see dosageInstruction mapping</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest</t>
@@ -1595,14 +1612,7 @@
     <t>このエレメントはどのような量を表現するか定義するためにコンテキストにあわせてよく定義される。したがって、どのような単位でも利用することができる。使用されるコンテキストによってcomparatorエレメントで値が定義されることもある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>Supply.quantity[moodCode=RQO]</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.initialFill.duration</t>
@@ -1738,6 +1748,15 @@
   </si>
   <si>
     <t>1回の調剤で払い出される薬剤の量</t>
+  </si>
+  <si>
+    <t>Message/Body/NewRx/MedicationPrescribed/DaysSupply</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>RXD-4-Actual Dispense Amount / RXD-5.1-Actual Dispense Units.code / RXD-5.3-Actual Dispense Units.name of coding system</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration</t>
@@ -2351,7 +2370,7 @@
   <cols>
     <col min="1" max="1" width="69.44921875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="69.44921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="24.5703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="28.5078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -3664,33 +3683,33 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>82</v>
@@ -3715,13 +3734,13 @@
         <v>149</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3786,27 +3805,27 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3829,13 +3848,13 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3886,7 +3905,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3907,7 +3926,7 @@
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>82</v>
@@ -3918,10 +3937,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3950,7 +3969,7 @@
         <v>138</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>140</v>
@@ -3991,10 +4010,10 @@
         <v>82</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>82</v>
@@ -4003,7 +4022,7 @@
         <v>154</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -4024,7 +4043,7 @@
         <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>82</v>
@@ -4035,10 +4054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4064,16 +4083,16 @@
         <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -4098,13 +4117,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -4122,7 +4141,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4143,7 +4162,7 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
@@ -4154,10 +4173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4180,19 +4199,19 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -4217,13 +4236,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4241,7 +4260,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4262,21 +4281,21 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4302,23 +4321,23 @@
         <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>82</v>
@@ -4360,7 +4379,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4381,21 +4400,21 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4418,16 +4437,16 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4477,7 +4496,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4498,21 +4517,21 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4535,13 +4554,13 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4592,7 +4611,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4613,21 +4632,21 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4650,16 +4669,16 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4709,7 +4728,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4730,24 +4749,24 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
@@ -4757,7 +4776,7 @@
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
@@ -4772,13 +4791,13 @@
         <v>149</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4843,27 +4862,27 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4886,13 +4905,13 @@
         <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4943,7 +4962,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4964,7 +4983,7 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>82</v>
@@ -4975,10 +4994,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5007,7 +5026,7 @@
         <v>138</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>140</v>
@@ -5048,10 +5067,10 @@
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>82</v>
@@ -5060,7 +5079,7 @@
         <v>154</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5081,7 +5100,7 @@
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>82</v>
@@ -5092,10 +5111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5121,16 +5140,16 @@
         <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5155,13 +5174,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5179,7 +5198,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5200,7 +5219,7 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
@@ -5211,10 +5230,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5237,19 +5256,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5274,13 +5293,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5298,7 +5317,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5319,21 +5338,21 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5359,23 +5378,23 @@
         <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5417,7 +5436,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5438,21 +5457,21 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5475,16 +5494,16 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5534,7 +5553,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5555,21 +5574,21 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5592,13 +5611,13 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5649,7 +5668,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5670,21 +5689,21 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5707,16 +5726,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5766,7 +5785,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5787,24 +5806,24 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
@@ -5814,7 +5833,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5829,13 +5848,13 @@
         <v>149</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5900,27 +5919,27 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5943,13 +5962,13 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6000,7 +6019,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6021,7 +6040,7 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>82</v>
@@ -6032,10 +6051,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6064,7 +6083,7 @@
         <v>138</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>140</v>
@@ -6105,10 +6124,10 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
@@ -6117,7 +6136,7 @@
         <v>154</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6138,7 +6157,7 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
@@ -6149,10 +6168,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6178,16 +6197,16 @@
         <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6212,13 +6231,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6236,7 +6255,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6257,7 +6276,7 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
@@ -6268,10 +6287,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6294,19 +6313,19 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6331,13 +6350,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6355,7 +6374,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6376,21 +6395,21 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6416,23 +6435,23 @@
         <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6474,7 +6493,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6495,21 +6514,21 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6532,16 +6551,16 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6591,7 +6610,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6612,21 +6631,21 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6649,13 +6668,13 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6706,7 +6725,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6727,21 +6746,21 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6764,16 +6783,16 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6823,7 +6842,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6844,21 +6863,21 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6884,13 +6903,13 @@
         <v>111</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6916,13 +6935,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6940,7 +6959,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>91</v>
@@ -6955,16 +6974,16 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6972,10 +6991,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6998,16 +7017,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7033,13 +7052,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7057,7 +7076,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7072,13 +7091,13 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -7089,10 +7108,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7118,13 +7137,13 @@
         <v>111</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7150,13 +7169,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7174,7 +7193,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>91</v>
@@ -7189,16 +7208,16 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7206,10 +7225,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7232,16 +7251,16 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7271,7 +7290,7 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7289,7 +7308,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7307,13 +7326,13 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7321,10 +7340,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7350,13 +7369,13 @@
         <v>111</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7382,13 +7401,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7406,7 +7425,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7421,16 +7440,16 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7438,10 +7457,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7464,16 +7483,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7523,7 +7542,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7544,7 +7563,7 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
@@ -7555,10 +7574,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7581,13 +7600,13 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7638,7 +7657,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7659,7 +7678,7 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7670,10 +7689,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7696,16 +7715,16 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7755,7 +7774,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>91</v>
@@ -7770,27 +7789,27 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7813,16 +7832,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7872,7 +7891,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>91</v>
@@ -7887,27 +7906,27 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7930,16 +7949,16 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7989,7 +8008,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8004,27 +8023,27 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8047,16 +8066,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8106,7 +8125,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8121,16 +8140,16 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8138,10 +8157,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8164,13 +8183,13 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8221,7 +8240,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8236,27 +8255,27 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8279,16 +8298,16 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8338,7 +8357,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8353,16 +8372,16 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8370,10 +8389,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8396,16 +8415,16 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8455,7 +8474,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8470,16 +8489,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8487,10 +8506,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8513,16 +8532,16 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8548,11 +8567,11 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8570,7 +8589,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8585,13 +8604,13 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8602,10 +8621,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8628,16 +8647,16 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8687,7 +8706,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8708,10 +8727,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8719,10 +8738,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8745,16 +8764,16 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8780,13 +8799,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8804,7 +8823,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8819,27 +8838,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8862,16 +8881,16 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8921,7 +8940,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8936,16 +8955,16 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8953,10 +8972,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8979,16 +8998,16 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9038,7 +9057,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9053,13 +9072,13 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>82</v>
@@ -9070,10 +9089,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9099,13 +9118,13 @@
         <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9155,7 +9174,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9176,7 +9195,7 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>82</v>
@@ -9187,10 +9206,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9213,16 +9232,16 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9272,7 +9291,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9287,13 +9306,13 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>82</v>
@@ -9304,10 +9323,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9333,14 +9352,14 @@
         <v>149</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9389,7 +9408,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9404,13 +9423,13 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>82</v>
@@ -9421,10 +9440,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9447,16 +9466,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9482,13 +9501,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9506,7 +9525,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9527,7 +9546,7 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>82</v>
@@ -9538,10 +9557,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9564,16 +9583,16 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9623,7 +9642,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9638,13 +9657,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9655,10 +9674,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9681,16 +9700,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9740,7 +9759,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9755,13 +9774,13 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>82</v>
@@ -9772,10 +9791,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9798,16 +9817,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9857,7 +9876,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9872,13 +9891,13 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>82</v>
+        <v>460</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>82</v>
@@ -9889,10 +9908,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9915,13 +9934,13 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9972,7 +9991,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9990,10 +10009,10 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>82</v>
@@ -10004,10 +10023,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10030,13 +10049,13 @@
         <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10087,7 +10106,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10108,7 +10127,7 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10119,10 +10138,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10148,10 +10167,10 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10190,7 +10209,7 @@
         <v>82</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC67" s="2"/>
       <c r="AD67" t="s" s="2">
@@ -10200,7 +10219,7 @@
         <v>154</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10232,13 +10251,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="B68" t="s" s="2">
-        <v>468</v>
-      </c>
       <c r="C68" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>82</v>
@@ -10260,13 +10279,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10317,7 +10336,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10326,7 +10345,7 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>142</v>
@@ -10349,13 +10368,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>82</v>
@@ -10377,13 +10396,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10434,7 +10453,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10443,7 +10462,7 @@
         <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>142</v>
@@ -10466,14 +10485,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10495,10 +10514,10 @@
         <v>137</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>140</v>
@@ -10553,7 +10572,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10585,10 +10604,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10611,16 +10630,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10670,7 +10689,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10691,7 +10710,7 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10702,10 +10721,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10728,13 +10747,13 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10785,7 +10804,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10806,7 +10825,7 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -10817,10 +10836,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10849,7 +10868,7 @@
         <v>138</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>140</v>
@@ -10902,7 +10921,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10923,7 +10942,7 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -10934,14 +10953,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10963,10 +10982,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -11021,7 +11040,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11053,10 +11072,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11079,16 +11098,16 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11138,7 +11157,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11147,10 +11166,10 @@
         <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>476</v>
+        <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>500</v>
+        <v>103</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11159,21 +11178,21 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11196,16 +11215,16 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11255,7 +11274,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11276,7 +11295,7 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11287,10 +11306,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11313,16 +11332,16 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11372,7 +11391,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11393,7 +11412,7 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -11404,10 +11423,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11430,19 +11449,19 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11491,7 +11510,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11509,10 +11528,10 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11523,10 +11542,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11549,13 +11568,13 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11606,7 +11625,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11627,7 +11646,7 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
@@ -11638,10 +11657,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11670,7 +11689,7 @@
         <v>138</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>140</v>
@@ -11711,10 +11730,10 @@
         <v>82</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>82</v>
@@ -11723,7 +11742,7 @@
         <v>154</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11744,7 +11763,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11755,10 +11774,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11781,16 +11800,16 @@
         <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11840,7 +11859,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11849,7 +11868,7 @@
         <v>91</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>103</v>
@@ -11861,21 +11880,21 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11898,23 +11917,23 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q82" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="R82" t="s" s="2">
         <v>82</v>
@@ -11959,7 +11978,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11968,7 +11987,7 @@
         <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>103</v>
@@ -11980,21 +11999,21 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12017,16 +12036,16 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12076,7 +12095,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12094,24 +12113,24 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12134,16 +12153,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12193,7 +12212,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12202,33 +12221,33 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>476</v>
+        <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>500</v>
+        <v>103</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>82</v>
+        <v>548</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>501</v>
+        <v>549</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>502</v>
+        <v>550</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12251,16 +12270,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12310,7 +12329,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12328,10 +12347,10 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12342,10 +12361,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12368,13 +12387,13 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12425,7 +12444,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12446,7 +12465,7 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12457,10 +12476,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12489,7 +12508,7 @@
         <v>138</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>140</v>
@@ -12530,10 +12549,10 @@
         <v>82</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>82</v>
@@ -12542,7 +12561,7 @@
         <v>154</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12563,7 +12582,7 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12574,10 +12593,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12600,19 +12619,19 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -12661,7 +12680,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12682,21 +12701,21 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12722,20 +12741,20 @@
         <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q89" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="R89" t="s" s="2">
         <v>82</v>
@@ -12756,13 +12775,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -12780,7 +12799,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12801,21 +12820,21 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12838,24 +12857,24 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>82</v>
@@ -12897,7 +12916,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12918,21 +12937,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12958,21 +12977,21 @@
         <v>105</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>82</v>
@@ -13014,7 +13033,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13023,7 +13042,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13035,21 +13054,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13075,23 +13094,23 @@
         <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>82</v>
@@ -13133,7 +13152,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13154,21 +13173,21 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13191,16 +13210,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13250,7 +13269,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13271,10 +13290,10 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13282,10 +13301,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13308,13 +13327,13 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13365,7 +13384,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13383,10 +13402,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13397,10 +13416,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13423,13 +13442,13 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13480,7 +13499,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13501,7 +13520,7 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>82</v>
@@ -13512,10 +13531,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13544,7 +13563,7 @@
         <v>138</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>140</v>
@@ -13597,7 +13616,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13618,7 +13637,7 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>82</v>
@@ -13629,14 +13648,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13658,10 +13677,10 @@
         <v>137</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>140</v>
@@ -13716,7 +13735,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13748,10 +13767,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13774,16 +13793,16 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13813,7 +13832,7 @@
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13831,7 +13850,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>91</v>
@@ -13849,24 +13868,24 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13889,16 +13908,16 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13924,31 +13943,31 @@
         <v>82</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Y99" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF99" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13966,24 +13985,24 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14006,16 +14025,16 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14065,7 +14084,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14080,13 +14099,13 @@
         <v>103</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
@@ -14097,14 +14116,14 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14123,16 +14142,16 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14182,7 +14201,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14203,7 +14222,7 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
@@ -14214,10 +14233,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14240,16 +14259,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14299,7 +14318,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14314,13 +14333,13 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -824,7 +824,7 @@
     <t>prescriptionIdentifierCommon</t>
   </si>
   <si>
-    <t>処方箋に対するID</t>
+    <t>全国で⼀意となる処方箋ID</t>
   </si>
   <si>
     <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
@@ -1017,8 +1017,8 @@
     <t>MedicationRequest.reported[x]</t>
   </si>
   <si>
-    <t>boolean
-Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)</t>
+    <t xml:space="preserve">Reference(Patient|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|RelatedPerson|Organization|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+</t>
   </si>
   <si>
     <t>初期記録にはない報告</t>
@@ -1045,7 +1045,7 @@
   <si>
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the medication resource is recommended.  For example, if you require form or lot number, then you must reference the Medication resource.  
 ひとつのtext要素と、複数のcoding 要素を記述できる。処方オーダ時に選択または入力し、実際に処方箋に印字される文字列を必ずtext要素に格納した上で、それをコード化した情報を1個以上のcoding 要素に記述する。  
-厚生労働省標準であるHOT9コード（販社指定が不要な場合にはHOT7コード）または広く流通しているYJコードを用いるか、一般名処方の場合には厚生労働省保険局一般名処方マスタのコードを使用して、Coding要素（コードsystemを識別するURI、医薬品のコード、そのコード表における医薬品の名称の3つからなる）で記述する。  
+厚生労働省標準であるHOT9コード、HOT13コード（販社指定が不要な場合にはHOT7コード）または広く流通しているYJコードを用いるか、一般名処方の場合には厚生労働省保険局一般名処方マスタのコードを使用して、Coding要素（コードsystemを識別するURI、医薬品のコード、そのコード表における医薬品の名称の3つからなる）で記述する。  
 なお、上記のいずれの標準的コードも付番されていない医薬品や医療材料の場合には、薬機法の下で使用されているGS1標準の識別コードであるGTIN(Global Trade Item Number)の調剤包装単位（最少包装単位、個別包装単位）14桁を使用する。  
 ひとつの処方薬、医療材料を複数のコード体系のコードで記述してもよく、その場合にcoding 要素を繰り返して記述する。  
 ただし、ひとつの処方薬を複数のコードで繰り返し記述する場合には、それらのコードが指し示す処方薬、医療材料は当然同一でなければならない。  
@@ -1166,7 +1166,7 @@
 </t>
   </si>
   <si>
-    <t>この処方オーダが最初に記述された日</t>
+    <t>この処方オーダが最初に記述された日時</t>
   </si>
   <si>
     <t>JP Coreでは必須。処方指示が最初に作成された日時。秒の精度まで記録する。タイムゾーンも付与しなければならない。</t>
@@ -1360,7 +1360,7 @@
     <t>MedicationRequest.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|MedicationRequest|ServiceRequest|ImmunizationRecommendation)
+    <t xml:space="preserve">Reference(CarePlan|http://jpfhir.jp/fhir/core/StructureDefinition/JP_CarePlan|MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|ServiceRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_ServiceRequest_Common|ImmunizationRecommendation)
 </t>
   </si>
   <si>
@@ -1814,7 +1814,7 @@
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.comparator</t>
   </si>
   <si>
-    <t>&lt;|&lt;= |&gt; = |&gt;  - 価値を理解する方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+    <t>&lt;|&lt;= |&gt; = |&gt;  - 値の比較方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
   </si>
   <si>
     <t>値をどのように理解し、表現する必要があるか - 測定の問題により実際の値が記載されている値よりも大きいか小さいかどうか。例えばコンパレータが「&lt;」の場合、実際の値は&lt;stated値です。 / How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
@@ -1826,7 +1826,7 @@
     <t>コンパレータがない場合、値の変更はありません / If there is no comparator, then there is no modification of the value</t>
   </si>
   <si>
-    <t>量を理解し、表現する方法。 / How the Quantity should be understood and represented.</t>
+    <t>数量の評価解釈コード / How the Quantity should be understood and represented.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -2368,17 +2368,17 @@
   <dimension ref="A1:AO102"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="69.44921875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="69.44921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="28.5078125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="59.5390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="59.5390625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="24.44140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="244.94140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2387,27 +2387,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="178.55859375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="75.55078125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="59.37890625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="153.08203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.76953125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="50.90625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="128.41796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="245.42578125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="110.09375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -374,7 +374,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -645,7 +645,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -739,7 +739,7 @@
     <t>MedicationRequest.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -902,7 +902,7 @@
     <t>特定のステータスの理由を特定します。 / Identifies the reasons for a given status.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Request.statusReason</t>
@@ -1140,7 +1140,7 @@
     <t>MedicationRequest.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1286,7 +1286,7 @@
     <t>薬が注文された理由を示すコード化された概念。 / A coded concept indicating why the medication was ordered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1409,7 +1409,7 @@
     <t>投薬投与の全体的なパターンを特定します。 / Identifies the overall pattern of medication administratio.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy|4.0.1</t>
   </si>
   <si>
     <t>Act.code where classCode = LIST and moodCode = EVN</t>
@@ -2003,7 +2003,7 @@
     <t>MedicationRequest.priorPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -2026,7 +2026,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -2045,7 +2045,7 @@
     <t>MedicationRequest.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
